--- a/exports/trend_1d/TCS_full_report.xlsx
+++ b/exports/trend_1d/TCS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>1286.88</v>
+        <v>1256.55</v>
       </c>
       <c r="I2" t="n">
         <v>1279.679417117889</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>1.37</v>
+        <v>-1.02</v>
       </c>
       <c r="L2" t="n">
         <v>4.18</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42145</v>
+        <v>42146</v>
       </c>
       <c r="H3" t="n">
-        <v>1277.75</v>
+        <v>1308.95</v>
       </c>
       <c r="I3" t="n">
         <v>1307.530918721474</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.69</v>
+        <v>-4.17</v>
       </c>
       <c r="L3" t="n">
         <v>7.99</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42194</v>
+        <v>42195</v>
       </c>
       <c r="H4" t="n">
-        <v>1261.25</v>
+        <v>1237.18</v>
       </c>
       <c r="I4" t="n">
         <v>1243.935893306675</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.64</v>
+        <v>-5.48</v>
       </c>
       <c r="L4" t="n">
-        <v>5.39</v>
+        <v>6.22</v>
       </c>
       <c r="M4" t="n">
         <v>0.91</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H5" t="n">
-        <v>1302.1</v>
+        <v>1335.85</v>
       </c>
       <c r="I5" t="n">
         <v>1308.404274576648</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.25</v>
+        <v>-7.98</v>
       </c>
       <c r="L5" t="n">
-        <v>5.48</v>
+        <v>8.77</v>
       </c>
       <c r="M5" t="n">
         <v>1.45</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="O5" t="n">
         <v>-1.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>6.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H6" t="n">
-        <v>1289.33</v>
+        <v>1283.58</v>
       </c>
       <c r="I6" t="n">
         <v>1287.547235212465</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.48</v>
+        <v>-3.91</v>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="M6" t="n">
         <v>1.39</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.07</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H7" t="n">
-        <v>1322.3</v>
+        <v>1355.83</v>
       </c>
       <c r="I7" t="n">
         <v>1337.785350167617</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.02</v>
+        <v>-5.63</v>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
         <v>2.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
         <v>-0.45</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.68</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42290</v>
+        <v>42291</v>
       </c>
       <c r="H8" t="n">
-        <v>1299.28</v>
+        <v>1241.85</v>
       </c>
       <c r="I8" t="n">
         <v>1265.317780605414</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.17</v>
+        <v>-8.41</v>
       </c>
       <c r="L8" t="n">
-        <v>5.31</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.22</v>
+        <v>1.95</v>
       </c>
       <c r="N8" t="n">
-        <v>1.71</v>
+        <v>4.42</v>
       </c>
       <c r="O8" t="n">
         <v>2.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.94</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42354</v>
+        <v>42355</v>
       </c>
       <c r="H9" t="n">
-        <v>1204.2</v>
+        <v>1219.88</v>
       </c>
       <c r="I9" t="n">
         <v>1215.898053571377</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K9" t="n">
-        <v>3.03</v>
+        <v>1.77</v>
       </c>
       <c r="L9" t="n">
         <v>2.63</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>5.48</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42380</v>
+        <v>42381</v>
       </c>
       <c r="H10" t="n">
-        <v>1181.18</v>
+        <v>1163.53</v>
       </c>
       <c r="I10" t="n">
         <v>1172.604303490773</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.17</v>
+        <v>-4.62</v>
       </c>
       <c r="L10" t="n">
-        <v>4.05</v>
+        <v>5.66</v>
       </c>
       <c r="M10" t="n">
         <v>0.8100000000000001</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.53</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H11" t="n">
-        <v>1165.6</v>
+        <v>1195.65</v>
       </c>
       <c r="I11" t="n">
         <v>1194.182175957065</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.18</v>
+        <v>-2.76</v>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>3.13</v>
       </c>
       <c r="M11" t="n">
-        <v>0.82</v>
+        <v>1.18</v>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
         <v>-1.49</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.72</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42408</v>
+        <v>42409</v>
       </c>
       <c r="H12" t="n">
-        <v>1181.48</v>
+        <v>1140.7</v>
       </c>
       <c r="I12" t="n">
         <v>1142.060302586962</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.19</v>
+        <v>-4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>2.35</v>
+        <v>5.67</v>
       </c>
       <c r="M12" t="n">
-        <v>0.91</v>
+        <v>1.24</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>2.58</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.84</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H13" t="n">
-        <v>1159.43</v>
+        <v>1186.58</v>
       </c>
       <c r="I13" t="n">
         <v>1178.009512608208</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.64</v>
+        <v>-4.02</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
         <v>1.24</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.91</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="H14" t="n">
-        <v>1286.98</v>
+        <v>1247.93</v>
       </c>
       <c r="I14" t="n">
         <v>1256.335076326458</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K14" t="n">
-        <v>8.460000000000001</v>
+        <v>5.17</v>
       </c>
       <c r="L14" t="n">
         <v>3.29</v>
@@ -1239,7 +1406,7 @@
         <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
         <v>2.34</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.84</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42578</v>
+        <v>42579</v>
       </c>
       <c r="H15" t="n">
-        <v>1288.78</v>
+        <v>1309.63</v>
       </c>
       <c r="I15" t="n">
         <v>1290.953280179586</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.27</v>
+        <v>-4.94</v>
       </c>
       <c r="L15" t="n">
-        <v>3.39</v>
+        <v>5.36</v>
       </c>
       <c r="M15" t="n">
         <v>0.76</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>6.26</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42601</v>
+        <v>42604</v>
       </c>
       <c r="H16" t="n">
-        <v>1301.75</v>
+        <v>1274.35</v>
       </c>
       <c r="I16" t="n">
         <v>1286.939734218312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6</v>
+        <v>-2.69</v>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>3.17</v>
       </c>
       <c r="M16" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="N16" t="n">
         <v>2.49</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42698</v>
+        <v>42699</v>
       </c>
       <c r="H17" t="n">
-        <v>1094.23</v>
+        <v>1150.18</v>
       </c>
       <c r="I17" t="n">
         <v>1149.918085185642</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" t="n">
-        <v>14.13</v>
+        <v>9.74</v>
       </c>
       <c r="L17" t="n">
         <v>2.21</v>
@@ -1410,7 +1613,7 @@
         <v>1.61</v>
       </c>
       <c r="N17" t="n">
-        <v>3.22</v>
+        <v>5.11</v>
       </c>
       <c r="O17" t="n">
         <v>-2.1</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42747</v>
+        <v>42748</v>
       </c>
       <c r="H18" t="n">
-        <v>1172.18</v>
+        <v>1124.65</v>
       </c>
       <c r="I18" t="n">
         <v>1125.222385089869</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" t="n">
-        <v>1.91</v>
+        <v>-2.22</v>
       </c>
       <c r="L18" t="n">
         <v>6.73</v>
@@ -1467,7 +1682,7 @@
         <v>0.97</v>
       </c>
       <c r="N18" t="n">
-        <v>2.27</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
         <v>5.11</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42775</v>
+        <v>42776</v>
       </c>
       <c r="H19" t="n">
-        <v>1158.65</v>
+        <v>1198.98</v>
       </c>
       <c r="I19" t="n">
         <v>1177.630633694231</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.02</v>
+        <v>-6.61</v>
       </c>
       <c r="L19" t="n">
-        <v>5.76</v>
+        <v>7.79</v>
       </c>
       <c r="M19" t="n">
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>3.48</v>
       </c>
       <c r="O19" t="n">
         <v>-4.05</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42817</v>
+        <v>42818</v>
       </c>
       <c r="H20" t="n">
-        <v>1230.18</v>
+        <v>1213.6</v>
       </c>
       <c r="I20" t="n">
         <v>1217.756781151302</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>1.22</v>
       </c>
       <c r="L20" t="n">
         <v>3.63</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H21" t="n">
-        <v>1182.55</v>
+        <v>1214.58</v>
       </c>
       <c r="I21" t="n">
         <v>1207.961005184025</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
-        <v>2.56</v>
+        <v>-0.08</v>
       </c>
       <c r="L21" t="n">
         <v>1.76</v>
@@ -1638,7 +1889,7 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>2.07</v>
+        <v>2.71</v>
       </c>
       <c r="O21" t="n">
         <v>-1.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.45</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H22" t="n">
-        <v>1253.5</v>
+        <v>1243.6</v>
       </c>
       <c r="I22" t="n">
         <v>1251.665419419141</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="L22" t="n">
         <v>2.29</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.8</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42926</v>
+        <v>42927</v>
       </c>
       <c r="H23" t="n">
-        <v>1217.48</v>
+        <v>1237.9</v>
       </c>
       <c r="I23" t="n">
         <v>1234.165613683524</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="M23" t="n">
         <v>0.72</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.69</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43082</v>
+        <v>43083</v>
       </c>
       <c r="H24" t="n">
-        <v>1314.2</v>
+        <v>1278.9</v>
       </c>
       <c r="I24" t="n">
         <v>1289.931735908032</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K24" t="n">
-        <v>6.16</v>
+        <v>3.31</v>
       </c>
       <c r="L24" t="n">
         <v>4.07</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H25" t="n">
-        <v>1344.6</v>
+        <v>1357.2</v>
       </c>
       <c r="I25" t="n">
         <v>1353.663053566586</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.14</v>
+        <v>-6.12</v>
       </c>
       <c r="L25" t="n">
-        <v>5.91</v>
+        <v>6.61</v>
       </c>
       <c r="M25" t="n">
         <v>1.48</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.93</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43143</v>
+        <v>43145</v>
       </c>
       <c r="H26" t="n">
-        <v>1483.65</v>
+        <v>1455.9</v>
       </c>
       <c r="I26" t="n">
         <v>1455.934359006975</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>9.32</v>
+        <v>7.27</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.69</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43200</v>
+        <v>43201</v>
       </c>
       <c r="H27" t="n">
-        <v>1468.8</v>
+        <v>1507.08</v>
       </c>
       <c r="I27" t="n">
         <v>1491.698656484803</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.89</v>
+        <v>-3.52</v>
       </c>
       <c r="L27" t="n">
         <v>7.39</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H28" t="n">
-        <v>2162.85</v>
+        <v>2064.8</v>
       </c>
       <c r="I28" t="n">
         <v>2081.94006996487</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K28" t="n">
-        <v>43.51</v>
+        <v>37.01</v>
       </c>
       <c r="L28" t="n">
         <v>2.27</v>
@@ -2037,7 +2372,7 @@
         <v>1.31</v>
       </c>
       <c r="N28" t="n">
-        <v>4.11</v>
+        <v>4.53</v>
       </c>
       <c r="O28" t="n">
         <v>2.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.81</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43431</v>
+        <v>43432</v>
       </c>
       <c r="H29" t="n">
-        <v>1890.25</v>
+        <v>1983.9</v>
       </c>
       <c r="I29" t="n">
         <v>1978.492983314885</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K29" t="n">
-        <v>8.449999999999999</v>
+        <v>3.92</v>
       </c>
       <c r="L29" t="n">
         <v>4.45</v>
@@ -2094,7 +2441,7 @@
         <v>1.46</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="O29" t="n">
         <v>-4.53</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>11.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43475</v>
+        <v>43476</v>
       </c>
       <c r="H30" t="n">
-        <v>1888.55</v>
+        <v>1842.55</v>
       </c>
       <c r="I30" t="n">
         <v>1867.563734372894</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.81</v>
+        <v>-7.12</v>
       </c>
       <c r="L30" t="n">
-        <v>7.2</v>
+        <v>7.51</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>7.41</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H31" t="n">
-        <v>1920.8</v>
+        <v>1955</v>
       </c>
       <c r="I31" t="n">
         <v>1954.535707951742</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.25</v>
+        <v>-6.1</v>
       </c>
       <c r="L31" t="n">
-        <v>5.02</v>
+        <v>6.48</v>
       </c>
       <c r="M31" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="N31" t="n">
         <v>3.01</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.27</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43511</v>
+        <v>43514</v>
       </c>
       <c r="H32" t="n">
-        <v>2029.7</v>
+        <v>1970.3</v>
       </c>
       <c r="I32" t="n">
         <v>1972.169235971977</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>3.82</v>
+        <v>0.78</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -2265,7 +2648,7 @@
         <v>0.38</v>
       </c>
       <c r="N32" t="n">
-        <v>1.03</v>
+        <v>2.93</v>
       </c>
       <c r="O32" t="n">
         <v>1.78</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43522</v>
+        <v>43523</v>
       </c>
       <c r="H33" t="n">
-        <v>2038.7</v>
+        <v>2058.1</v>
       </c>
       <c r="I33" t="n">
         <v>2049.647255111755</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.47</v>
+        <v>-4.46</v>
       </c>
       <c r="L33" t="n">
-        <v>3.8</v>
+        <v>5.31</v>
       </c>
       <c r="M33" t="n">
         <v>0.54</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.71</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H34" t="n">
-        <v>2128.75</v>
+        <v>2092.35</v>
       </c>
       <c r="I34" t="n">
         <v>2118.427352520091</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K34" t="n">
-        <v>3.43</v>
+        <v>1.66</v>
       </c>
       <c r="L34" t="n">
         <v>4.86</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43616</v>
+        <v>43619</v>
       </c>
       <c r="H35" t="n">
-        <v>2196.55</v>
+        <v>2242.3</v>
       </c>
       <c r="I35" t="n">
         <v>2207.281126718324</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.98</v>
+        <v>-7.17</v>
       </c>
       <c r="L35" t="n">
-        <v>5.38</v>
+        <v>7.42</v>
       </c>
       <c r="M35" t="n">
         <v>1.41</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>8.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H36" t="n">
-        <v>2175.4</v>
+        <v>2133.35</v>
       </c>
       <c r="I36" t="n">
         <v>2138.816943438897</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.98</v>
+        <v>-4.86</v>
       </c>
       <c r="L36" t="n">
-        <v>4.91</v>
+        <v>6.14</v>
       </c>
       <c r="M36" t="n">
         <v>1.32</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43679</v>
+        <v>43682</v>
       </c>
       <c r="H37" t="n">
-        <v>2205.3</v>
+        <v>2248.6</v>
       </c>
       <c r="I37" t="n">
         <v>2216.59668227414</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.37</v>
+        <v>-5.4</v>
       </c>
       <c r="L37" t="n">
-        <v>3.94</v>
+        <v>5.57</v>
       </c>
       <c r="M37" t="n">
         <v>0.9399999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.49</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43724</v>
+        <v>43725</v>
       </c>
       <c r="H38" t="n">
-        <v>2150</v>
+        <v>2122.65</v>
       </c>
       <c r="I38" t="n">
         <v>2126.25306696441</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.38</v>
+        <v>-5.6</v>
       </c>
       <c r="L38" t="n">
-        <v>5.92</v>
+        <v>6.36</v>
       </c>
       <c r="M38" t="n">
         <v>0.83</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.71</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43762</v>
+        <v>43763</v>
       </c>
       <c r="H39" t="n">
-        <v>2082</v>
+        <v>2124.95</v>
       </c>
       <c r="I39" t="n">
         <v>2111.951937480096</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>1.92</v>
+        <v>-0.11</v>
       </c>
       <c r="L39" t="n">
         <v>1.6</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.81</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43777</v>
+        <v>43780</v>
       </c>
       <c r="H40" t="n">
-        <v>2129.95</v>
+        <v>2100.95</v>
       </c>
       <c r="I40" t="n">
         <v>2104.663632143481</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>0.24</v>
+        <v>-1.13</v>
       </c>
       <c r="L40" t="n">
         <v>2.35</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>7.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43817</v>
+        <v>43818</v>
       </c>
       <c r="H41" t="n">
-        <v>2167.75</v>
+        <v>2229.05</v>
       </c>
       <c r="I41" t="n">
         <v>2170.523457096257</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.18</v>
+        <v>-6.1</v>
       </c>
       <c r="L41" t="n">
-        <v>5.26</v>
+        <v>6.45</v>
       </c>
       <c r="M41" t="n">
         <v>1.19</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.76</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H42" t="n">
-        <v>2137.85</v>
+        <v>2079.05</v>
       </c>
       <c r="I42" t="n">
         <v>2110.449961100096</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.09</v>
+        <v>-6.73</v>
       </c>
       <c r="L42" t="n">
-        <v>4.67</v>
+        <v>7.06</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
         <v>2.83</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H43" t="n">
-        <v>1905.65</v>
+        <v>2014.45</v>
       </c>
       <c r="I43" t="n">
         <v>1951.591915437336</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K43" t="n">
-        <v>8.34</v>
+        <v>3.11</v>
       </c>
       <c r="L43" t="n">
         <v>7.26</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.58</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H44" t="n">
-        <v>2467.45</v>
+        <v>2332.25</v>
       </c>
       <c r="I44" t="n">
         <v>2332.915321875103</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K44" t="n">
-        <v>22.49</v>
+        <v>15.78</v>
       </c>
       <c r="L44" t="n">
         <v>7.41</v>
@@ -2949,7 +3476,7 @@
         <v>2.73</v>
       </c>
       <c r="N44" t="n">
-        <v>4.17</v>
+        <v>5.48</v>
       </c>
       <c r="O44" t="n">
         <v>5.71</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.45</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H45" t="n">
-        <v>2523.45</v>
+        <v>2705.8</v>
       </c>
       <c r="I45" t="n">
         <v>2599.369291044637</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.199999999999999</v>
+        <v>-16.02</v>
       </c>
       <c r="L45" t="n">
-        <v>8.91</v>
+        <v>16.97</v>
       </c>
       <c r="M45" t="n">
-        <v>1.53</v>
+        <v>3.83</v>
       </c>
       <c r="N45" t="n">
-        <v>3.86</v>
+        <v>7.23</v>
       </c>
       <c r="O45" t="n">
         <v>-5.48</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.97</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44243</v>
+        <v>44244</v>
       </c>
       <c r="H46" t="n">
-        <v>3108.8</v>
+        <v>3073.1</v>
       </c>
       <c r="I46" t="n">
         <v>3097.231922173727</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K46" t="n">
-        <v>14.89</v>
+        <v>13.57</v>
       </c>
       <c r="L46" t="n">
         <v>3.91</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.7</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44285</v>
+        <v>44286</v>
       </c>
       <c r="H47" t="n">
-        <v>3158.55</v>
+        <v>3177.85</v>
       </c>
       <c r="I47" t="n">
         <v>3176.816037879847</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.78</v>
+        <v>-3.41</v>
       </c>
       <c r="L47" t="n">
-        <v>3.75</v>
+        <v>4.29</v>
       </c>
       <c r="M47" t="n">
         <v>1.22</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44298</v>
+        <v>44299</v>
       </c>
       <c r="H48" t="n">
-        <v>3246.55</v>
+        <v>3104.05</v>
       </c>
       <c r="I48" t="n">
         <v>3113.770444713651</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>2.16</v>
+        <v>-2.32</v>
       </c>
       <c r="L48" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="M48" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.28</v>
+        <v>4.39</v>
       </c>
       <c r="O48" t="n">
         <v>0.61</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44357</v>
+        <v>44358</v>
       </c>
       <c r="H49" t="n">
-        <v>3216.8</v>
+        <v>3273.8</v>
       </c>
       <c r="I49" t="n">
         <v>3229.230462546668</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.63</v>
+        <v>-5.47</v>
       </c>
       <c r="L49" t="n">
-        <v>4.61</v>
+        <v>6.6</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>5.01</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
       <c r="H50" t="n">
-        <v>3193.1</v>
+        <v>3187.55</v>
       </c>
       <c r="I50" t="n">
         <v>3193.067218960182</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.47</v>
+        <v>-2.63</v>
       </c>
       <c r="L50" t="n">
-        <v>2.61</v>
+        <v>3.02</v>
       </c>
       <c r="M50" t="n">
         <v>0.98</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.47</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44414</v>
+        <v>44417</v>
       </c>
       <c r="H51" t="n">
-        <v>3309.8</v>
+        <v>3322.7</v>
       </c>
       <c r="I51" t="n">
         <v>3311.68026284522</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.84</v>
+        <v>-4.24</v>
       </c>
       <c r="L51" t="n">
-        <v>4.28</v>
+        <v>4.69</v>
       </c>
       <c r="M51" t="n">
         <v>0.73</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.41</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44477</v>
+        <v>44480</v>
       </c>
       <c r="H52" t="n">
-        <v>3935.65</v>
+        <v>3685.6</v>
       </c>
       <c r="I52" t="n">
         <v>3704.690720779234</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K52" t="n">
-        <v>18.45</v>
+        <v>10.92</v>
       </c>
       <c r="L52" t="n">
         <v>0.38</v>
       </c>
       <c r="M52" t="n">
-        <v>1.53</v>
+        <v>4.59</v>
       </c>
       <c r="N52" t="n">
-        <v>1.93</v>
+        <v>6.35</v>
       </c>
       <c r="O52" t="n">
         <v>0.39</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44531</v>
+        <v>44532</v>
       </c>
       <c r="H53" t="n">
-        <v>3577.8</v>
+        <v>3642.9</v>
       </c>
       <c r="I53" t="n">
         <v>3624.5045030989</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>2.92</v>
+        <v>1.16</v>
       </c>
       <c r="L53" t="n">
         <v>1.95</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.43</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H54" t="n">
-        <v>3833.5</v>
+        <v>3771.35</v>
       </c>
       <c r="I54" t="n">
         <v>3785.197048102197</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K54" t="n">
-        <v>5.23</v>
+        <v>3.53</v>
       </c>
       <c r="L54" t="n">
         <v>3.64</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.29</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44642</v>
+        <v>44643</v>
       </c>
       <c r="H55" t="n">
-        <v>3700.95</v>
+        <v>3712.4</v>
       </c>
       <c r="I55" t="n">
         <v>3709.517000930605</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K55" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="L55" t="n">
         <v>2.95</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.32</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H56" t="n">
-        <v>3661.95</v>
+        <v>3528.05</v>
       </c>
       <c r="I56" t="n">
         <v>3622.949732712371</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.36</v>
+        <v>-4.97</v>
       </c>
       <c r="L56" t="n">
-        <v>1.88</v>
+        <v>5.12</v>
       </c>
       <c r="M56" t="n">
-        <v>0.36</v>
+        <v>1.42</v>
       </c>
       <c r="N56" t="n">
-        <v>1.9</v>
+        <v>3.66</v>
       </c>
       <c r="O56" t="n">
         <v>0.31</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.22</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H57" t="n">
-        <v>3188.85</v>
+        <v>3260.5</v>
       </c>
       <c r="I57" t="n">
         <v>3228.356680535037</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K57" t="n">
-        <v>9.609999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="L57" t="n">
         <v>3.29</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44797</v>
+        <v>44798</v>
       </c>
       <c r="H58" t="n">
-        <v>3255.35</v>
+        <v>3218.2</v>
       </c>
       <c r="I58" t="n">
         <v>3236.330203815944</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.16</v>
+        <v>-1.3</v>
       </c>
       <c r="L58" t="n">
         <v>1.8</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.12</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44855</v>
+        <v>44858</v>
       </c>
       <c r="H59" t="n">
-        <v>3137.4</v>
+        <v>3161.7</v>
       </c>
       <c r="I59" t="n">
         <v>3160.859750205516</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="L59" t="n">
         <v>1.86</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.28</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H60" t="n">
-        <v>3305.1</v>
+        <v>3240.25</v>
       </c>
       <c r="I60" t="n">
         <v>3278.095781799489</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K60" t="n">
-        <v>4.54</v>
+        <v>2.48</v>
       </c>
       <c r="L60" t="n">
         <v>0.87</v>
@@ -3861,7 +4580,7 @@
         <v>1.43</v>
       </c>
       <c r="N60" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="O60" t="n">
         <v>0.77</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.15</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H61" t="n">
-        <v>3363.1</v>
+        <v>3414.9</v>
       </c>
       <c r="I61" t="n">
         <v>3392.227792284874</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.79</v>
+        <v>-5.39</v>
       </c>
       <c r="L61" t="n">
-        <v>5.21</v>
+        <v>5.52</v>
       </c>
       <c r="M61" t="n">
         <v>0.78</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.91</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H62" t="n">
-        <v>3400.45</v>
+        <v>3331.85</v>
       </c>
       <c r="I62" t="n">
         <v>3384.8877425676</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.42</v>
+        <v>-2.43</v>
       </c>
       <c r="L62" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="M62" t="n">
         <v>1.04</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.89</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45054</v>
+        <v>45055</v>
       </c>
       <c r="H63" t="n">
-        <v>3250.6</v>
+        <v>3283.25</v>
       </c>
       <c r="I63" t="n">
         <v>3281.520234896147</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K63" t="n">
-        <v>2.44</v>
+        <v>1.46</v>
       </c>
       <c r="L63" t="n">
         <v>2.19</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>4.54</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45092</v>
+        <v>45093</v>
       </c>
       <c r="H64" t="n">
-        <v>3216.3</v>
+        <v>3174.9</v>
       </c>
       <c r="I64" t="n">
         <v>3198.834205903578</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.04</v>
+        <v>-3.3</v>
       </c>
       <c r="L64" t="n">
-        <v>2.69</v>
+        <v>3.88</v>
       </c>
       <c r="M64" t="n">
         <v>0.64</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>4.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45111</v>
+        <v>45112</v>
       </c>
       <c r="H65" t="n">
-        <v>3308.85</v>
+        <v>3319.95</v>
       </c>
       <c r="I65" t="n">
         <v>3312.47185724294</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.22</v>
+        <v>-4.57</v>
       </c>
       <c r="L65" t="n">
-        <v>4.53</v>
+        <v>4.85</v>
       </c>
       <c r="M65" t="n">
         <v>0.6899999999999999</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.04</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H66" t="n">
-        <v>3487.25</v>
+        <v>3455.65</v>
       </c>
       <c r="I66" t="n">
         <v>3472.745511830085</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K66" t="n">
-        <v>5.04</v>
+        <v>4.09</v>
       </c>
       <c r="L66" t="n">
         <v>2.1</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.77</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H67" t="n">
-        <v>3404.3</v>
+        <v>3497.85</v>
       </c>
       <c r="I67" t="n">
         <v>3467.886385511257</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>1.49</v>
+        <v>-1.22</v>
       </c>
       <c r="L67" t="n">
-        <v>1.27</v>
+        <v>2.13</v>
       </c>
       <c r="M67" t="n">
         <v>1.55</v>
       </c>
       <c r="N67" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="O67" t="n">
         <v>-0.91</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.37</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H68" t="n">
-        <v>3972.95</v>
+        <v>3910.9</v>
       </c>
       <c r="I68" t="n">
         <v>3946.706733465421</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K68" t="n">
-        <v>13.58</v>
+        <v>11.81</v>
       </c>
       <c r="L68" t="n">
         <v>2.39</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.99</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45469</v>
+        <v>45470</v>
       </c>
       <c r="H69" t="n">
-        <v>3855.85</v>
+        <v>3934.15</v>
       </c>
       <c r="I69" t="n">
         <v>3895.449141789254</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K69" t="n">
-        <v>1.41</v>
+        <v>-0.59</v>
       </c>
       <c r="L69" t="n">
         <v>3.92</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.46</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H70" t="n">
-        <v>4283.05</v>
+        <v>4155.05</v>
       </c>
       <c r="I70" t="n">
         <v>4157.713894063011</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K70" t="n">
-        <v>8.869999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="L70" t="n">
         <v>2.95</v>
       </c>
       <c r="M70" t="n">
-        <v>0.73</v>
+        <v>1.03</v>
       </c>
       <c r="N70" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="O70" t="n">
         <v>2.03</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.12</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45520</v>
+        <v>45523</v>
       </c>
       <c r="H71" t="n">
-        <v>4416.05</v>
+        <v>4490</v>
       </c>
       <c r="I71" t="n">
         <v>4450.988495808961</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.28</v>
+        <v>-8.06</v>
       </c>
       <c r="L71" t="n">
-        <v>6.55</v>
+        <v>8.16</v>
       </c>
       <c r="M71" t="n">
         <v>1.36</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.16</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H72" t="n">
-        <v>4346.15</v>
+        <v>4296.15</v>
       </c>
       <c r="I72" t="n">
         <v>4302.316947965473</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.2</v>
+        <v>-4.32</v>
       </c>
       <c r="L72" t="n">
-        <v>3.76</v>
+        <v>4.64</v>
       </c>
       <c r="M72" t="n">
         <v>1.02</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.58</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="H73" t="n">
-        <v>4147</v>
+        <v>4198.7</v>
       </c>
       <c r="I73" t="n">
         <v>4165.671874814539</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K73" t="n">
-        <v>3.47</v>
+        <v>2.27</v>
       </c>
       <c r="L73" t="n">
         <v>2.93</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.55</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H74" t="n">
-        <v>4271.9</v>
+        <v>4170.3</v>
       </c>
       <c r="I74" t="n">
         <v>4219.863372876138</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K74" t="n">
-        <v>1.74</v>
+        <v>-0.68</v>
       </c>
       <c r="L74" t="n">
         <v>4.97</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="H75" t="n">
-        <v>3443.5</v>
+        <v>3472.5</v>
       </c>
       <c r="I75" t="n">
         <v>3465.991807511627</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K75" t="n">
-        <v>17.43</v>
+        <v>16.73</v>
       </c>
       <c r="L75" t="n">
         <v>5.08</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>6.75</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H76" t="n">
-        <v>3382</v>
+        <v>3266</v>
       </c>
       <c r="I76" t="n">
         <v>3342.095997614647</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.61</v>
+        <v>-5.95</v>
       </c>
       <c r="L76" t="n">
-        <v>3.35</v>
+        <v>6.09</v>
       </c>
       <c r="M76" t="n">
-        <v>1.45</v>
+        <v>2.43</v>
       </c>
       <c r="N76" t="n">
-        <v>2.91</v>
+        <v>3.43</v>
       </c>
       <c r="O76" t="n">
         <v>0.84</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>5.89</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
       <c r="H77" t="n">
-        <v>3054</v>
+        <v>3140.6</v>
       </c>
       <c r="I77" t="n">
         <v>3135.255598099927</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K77" t="n">
-        <v>6.49</v>
+        <v>3.84</v>
       </c>
       <c r="L77" t="n">
         <v>2.11</v>
       </c>
       <c r="M77" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N77" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="O77" t="n">
         <v>-3.43</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>5.67</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H78" t="n">
-        <v>3062.4</v>
+        <v>3035.4</v>
       </c>
       <c r="I78" t="n">
         <v>3046.981410295041</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.49</v>
+        <v>-3.35</v>
       </c>
       <c r="L78" t="n">
         <v>3.97</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>4.88</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H79" t="n">
-        <v>3027.2</v>
+        <v>3061.7</v>
       </c>
       <c r="I79" t="n">
         <v>3042.795879998886</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K79" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
       <c r="L79" t="n">
-        <v>0.71</v>
+        <v>1.01</v>
       </c>
       <c r="M79" t="n">
         <v>0.58</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,25 +5939,25 @@
         <v>5.86</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H80" t="n">
-        <v>3206.7</v>
+        <v>3163.6</v>
       </c>
       <c r="I80" t="n">
         <v>3180.119233709633</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K80" t="n">
-        <v>4.74</v>
+        <v>3.33</v>
       </c>
       <c r="L80" t="n">
         <v>3.87</v>
       </c>
       <c r="M80" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="N80" t="n">
         <v>2.78</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>6.38</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H81" t="n">
-        <v>2539.8</v>
+        <v>2559.2</v>
       </c>
       <c r="I81" t="n">
         <v>2553.61736277408</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K81" t="n">
-        <v>19.72</v>
+        <v>19.1</v>
       </c>
       <c r="L81" t="n">
         <v>5.89</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>7.63</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H82" t="n">
-        <v>2521.8</v>
+        <v>2396.9</v>
       </c>
       <c r="I82" t="n">
         <v>2409.604131217669</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.46</v>
+        <v>-6.34</v>
       </c>
       <c r="L82" t="n">
-        <v>3.49</v>
+        <v>6.66</v>
       </c>
       <c r="M82" t="n">
         <v>1.36</v>
       </c>
       <c r="N82" t="n">
-        <v>2.76</v>
+        <v>4.95</v>
       </c>
       <c r="O82" t="n">
         <v>0.76</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>10.72</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H83" t="n">
-        <v>2297.4</v>
+        <v>2446.9</v>
       </c>
       <c r="I83" t="n">
         <v>2417.267009644154</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K83" t="n">
-        <v>4.15</v>
+        <v>-2.09</v>
       </c>
       <c r="L83" t="n">
         <v>4.51</v>
@@ -5172,7 +6167,7 @@
         <v>1.11</v>
       </c>
       <c r="N83" t="n">
-        <v>2.12</v>
+        <v>6.51</v>
       </c>
       <c r="O83" t="n">
         <v>-4.95</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>10.65</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H84" t="n">
-        <v>2198.9</v>
+        <v>2151.4</v>
       </c>
       <c r="I84" t="n">
         <v>2186.411954743349</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>-10.14</v>
+        <v>-12.08</v>
       </c>
       <c r="L84" t="n">
-        <v>10.42</v>
+        <v>12.41</v>
       </c>
       <c r="M84" t="n">
         <v>2.2</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>10.96</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="H85" t="n">
-        <v>2201</v>
+        <v>2269</v>
       </c>
       <c r="I85" t="n">
         <v>2203.18400025153</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K85" t="n">
-        <v>-2.31</v>
+        <v>-5.47</v>
       </c>
       <c r="L85" t="n">
-        <v>3.72</v>
+        <v>5.75</v>
       </c>
       <c r="M85" t="n">
         <v>2.72</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>9.84</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="H86" t="n">
-        <v>2270</v>
+        <v>2248.4</v>
       </c>
       <c r="I86" t="n">
         <v>2259.72844975458</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K86" t="n">
-        <v>0.04</v>
+        <v>-0.91</v>
       </c>
       <c r="L86" t="n">
         <v>3.32</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>7.75</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H87" t="n">
-        <v>2125</v>
+        <v>2269.3</v>
       </c>
       <c r="I87" t="n">
         <v>2231.52581137236</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K87" t="n">
-        <v>5.49</v>
+        <v>-0.93</v>
       </c>
       <c r="L87" t="n">
         <v>6.71</v>
@@ -5400,7 +6443,7 @@
         <v>3.39</v>
       </c>
       <c r="N87" t="n">
-        <v>4.16</v>
+        <v>6.79</v>
       </c>
       <c r="O87" t="n">
         <v>-0.95</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5460,6 +6515,14 @@
       <c r="Q88" t="n">
         <v>11</v>
       </c>
+      <c r="R88" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10418,7 +11481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.3</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="6">
@@ -10428,7 +11491,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10438,7 +11501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -10448,7 +11511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10458,7 +11521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="10">
@@ -10468,7 +11531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.5</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="11">
@@ -10478,7 +11541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -10488,7 +11551,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -10498,7 +11561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="14">
@@ -10508,7 +11571,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.96</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="15">
@@ -10518,7 +11581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.95</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -10528,7 +11591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.96</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="17">
@@ -10538,7 +11601,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>43.51</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="18">
@@ -10548,7 +11611,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -10558,7 +11621,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.84</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
@@ -10568,7 +11631,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.74</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="21">
@@ -10578,7 +11641,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.42</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="22">
@@ -10588,7 +11651,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -10598,7 +11661,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -10608,7 +11671,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="25">
@@ -10628,7 +11691,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.03</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="27">
@@ -10648,7 +11711,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
